--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.01631448104413</v>
+      </c>
+      <c r="C2">
         <v>19.45191112492231</v>
-      </c>
-      <c r="C2">
-        <v>30.01631448104413</v>
       </c>
       <c r="D2">
         <v>5.140883040118218</v>
       </c>
       <c r="E2">
-        <v>13.01407777208926</v>
+        <v>20.08207052659755</v>
       </c>
       <c r="F2">
         <v>66.90385170131319</v>
       </c>
       <c r="G2">
-        <v>20.08207052659755</v>
+        <v>13.01407777208926</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.30199667221298</v>
+      </c>
+      <c r="C3">
         <v>17.24209650582363</v>
-      </c>
-      <c r="C3">
-        <v>31.30199667221298</v>
       </c>
       <c r="D3">
         <v>5.799758745476478</v>
       </c>
       <c r="E3">
-        <v>11.60739288714646</v>
+        <v>21.07252870344442</v>
       </c>
       <c r="F3">
         <v>67.32007840940913</v>
       </c>
       <c r="G3">
-        <v>21.07252870344442</v>
+        <v>11.60739288714646</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>41.0377358490566</v>
+      </c>
+      <c r="C4">
         <v>13.32547169811321</v>
-      </c>
-      <c r="C4">
-        <v>41.0377358490566</v>
       </c>
       <c r="D4">
         <v>7.504424778761062</v>
       </c>
       <c r="E4">
-        <v>8.632543926661576</v>
+        <v>26.58517952635599</v>
       </c>
       <c r="F4">
         <v>64.78227654698243</v>
       </c>
       <c r="G4">
-        <v>26.585179526356</v>
+        <v>8.632543926661574</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.18057663125948</v>
+      </c>
+      <c r="C5">
         <v>26.6818411734952</v>
-      </c>
-      <c r="C5">
-        <v>34.18057663125948</v>
       </c>
       <c r="D5">
         <v>3.747867298578199</v>
       </c>
       <c r="E5">
+        <v>21.24832953384168</v>
+      </c>
+      <c r="F5">
+        <v>62.16492414118386</v>
+      </c>
+      <c r="G5">
         <v>16.58674632497445</v>
-      </c>
-      <c r="F5">
-        <v>62.16492414118387</v>
-      </c>
-      <c r="G5">
-        <v>21.24832953384168</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>32.63279233525731</v>
+      </c>
+      <c r="C6">
         <v>17.27991847440213</v>
-      </c>
-      <c r="C6">
-        <v>32.63279233525731</v>
       </c>
       <c r="D6">
         <v>5.787064339923623</v>
       </c>
       <c r="E6">
-        <v>11.52665333117885</v>
+        <v>21.76786221729416</v>
       </c>
       <c r="F6">
         <v>66.70548445152698</v>
       </c>
       <c r="G6">
-        <v>21.76786221729416</v>
+        <v>11.52665333117885</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>35.55555555555556</v>
+      </c>
+      <c r="C7">
         <v>16.2962962962963</v>
-      </c>
-      <c r="C7">
-        <v>35.55555555555556</v>
       </c>
       <c r="D7">
         <v>6.136363636363637</v>
       </c>
       <c r="E7">
-        <v>10.73170731707317</v>
+        <v>23.41463414634147</v>
       </c>
       <c r="F7">
         <v>65.85365853658537</v>
       </c>
       <c r="G7">
-        <v>23.41463414634147</v>
+        <v>10.73170731707317</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>36.94509874977351</v>
+      </c>
+      <c r="C8">
         <v>15.14767167965211</v>
-      </c>
-      <c r="C8">
-        <v>36.94509874977351</v>
       </c>
       <c r="D8">
         <v>6.601674641148326</v>
       </c>
       <c r="E8">
-        <v>9.959494877293306</v>
+        <v>24.29116035263283</v>
       </c>
       <c r="F8">
         <v>65.74934477007386</v>
       </c>
       <c r="G8">
-        <v>24.29116035263283</v>
+        <v>9.959494877293306</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>34.86578585520416</v>
+      </c>
+      <c r="C9">
         <v>26.74119686734023</v>
-      </c>
-      <c r="C9">
-        <v>34.86578585520416</v>
       </c>
       <c r="D9">
         <v>3.739548401520233</v>
       </c>
       <c r="E9">
-        <v>16.54705534181711</v>
+        <v>21.57443030482391</v>
       </c>
       <c r="F9">
         <v>61.87851435335898</v>
       </c>
       <c r="G9">
-        <v>21.57443030482391</v>
+        <v>16.54705534181711</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>31.74502997791102</v>
+      </c>
+      <c r="C10">
         <v>18.04985799936889</v>
-      </c>
-      <c r="C10">
-        <v>31.74502997791102</v>
       </c>
       <c r="D10">
         <v>5.54020979020979</v>
       </c>
       <c r="E10">
+        <v>21.19233199915736</v>
+      </c>
+      <c r="F10">
+        <v>66.75795239098376</v>
+      </c>
+      <c r="G10">
         <v>12.04971560985886</v>
-      </c>
-      <c r="F10">
-        <v>66.75795239098377</v>
-      </c>
-      <c r="G10">
-        <v>21.19233199915736</v>
       </c>
     </row>
   </sheetData>
